--- a/extenbooks/S503.xlsx
+++ b/extenbooks/S503.xlsx
@@ -447,11 +447,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,6 +467,16 @@
           <t>S&amp;T 1994, units=billions_usd</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>, units=billions_usd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>BEA GDPbyIndustry, units=billions_usd</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -475,6 +487,16 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>S503-A</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>S503-COMBINED</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>S503-EXT</t>
         </is>
       </c>
     </row>
@@ -485,6 +507,12 @@
       <c r="B3" s="3" t="n">
         <v>247.74</v>
       </c>
+      <c r="C3" s="3" t="n">
+        <v>247.74</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -493,6 +521,12 @@
       <c r="B4" s="3" t="n">
         <v>242.9</v>
       </c>
+      <c r="C4" s="3" t="n">
+        <v>242.9</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -501,6 +535,12 @@
       <c r="B5" s="3" t="n">
         <v>269.06</v>
       </c>
+      <c r="C5" s="3" t="n">
+        <v>269.06</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -509,6 +549,12 @@
       <c r="B6" s="3" t="n">
         <v>307.03</v>
       </c>
+      <c r="C6" s="3" t="n">
+        <v>307.03</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -517,6 +563,12 @@
       <c r="B7" s="3" t="n">
         <v>319.61</v>
       </c>
+      <c r="C7" s="3" t="n">
+        <v>319.61</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -525,6 +577,12 @@
       <c r="B8" s="3" t="n">
         <v>336.71</v>
       </c>
+      <c r="C8" s="3" t="n">
+        <v>336.71</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -533,6 +591,12 @@
       <c r="B9" s="3" t="n">
         <v>335.2</v>
       </c>
+      <c r="C9" s="3" t="n">
+        <v>335.2</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -541,6 +605,12 @@
       <c r="B10" s="3" t="n">
         <v>365.74</v>
       </c>
+      <c r="C10" s="3" t="n">
+        <v>365.74</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -549,6 +619,12 @@
       <c r="B11" s="3" t="n">
         <v>384.1</v>
       </c>
+      <c r="C11" s="3" t="n">
+        <v>384.1</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -557,6 +633,12 @@
       <c r="B12" s="3" t="n">
         <v>402.67</v>
       </c>
+      <c r="C12" s="3" t="n">
+        <v>402.67</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -565,6 +647,12 @@
       <c r="B13" s="3" t="n">
         <v>403.67</v>
       </c>
+      <c r="C13" s="3" t="n">
+        <v>403.67</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -573,6 +661,12 @@
       <c r="B14" s="3" t="n">
         <v>439.36</v>
       </c>
+      <c r="C14" s="3" t="n">
+        <v>439.36</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -581,6 +675,12 @@
       <c r="B15" s="3" t="n">
         <v>451.95</v>
       </c>
+      <c r="C15" s="3" t="n">
+        <v>451.95</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -589,6 +689,12 @@
       <c r="B16" s="3" t="n">
         <v>463.88</v>
       </c>
+      <c r="C16" s="3" t="n">
+        <v>463.88</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -597,6 +703,12 @@
       <c r="B17" s="3" t="n">
         <v>498.12</v>
       </c>
+      <c r="C17" s="3" t="n">
+        <v>498.12</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -605,6 +717,12 @@
       <c r="B18" s="3" t="n">
         <v>523.74</v>
       </c>
+      <c r="C18" s="3" t="n">
+        <v>523.74</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -613,6 +731,12 @@
       <c r="B19" s="3" t="n">
         <v>561.05</v>
       </c>
+      <c r="C19" s="3" t="n">
+        <v>561.05</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -621,6 +745,12 @@
       <c r="B20" s="3" t="n">
         <v>609.78</v>
       </c>
+      <c r="C20" s="3" t="n">
+        <v>609.78</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -629,6 +759,12 @@
       <c r="B21" s="3" t="n">
         <v>665.9400000000001</v>
       </c>
+      <c r="C21" s="3" t="n">
+        <v>665.9400000000001</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -637,6 +773,12 @@
       <c r="B22" s="3" t="n">
         <v>699.15</v>
       </c>
+      <c r="C22" s="3" t="n">
+        <v>699.15</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -645,6 +787,12 @@
       <c r="B23" s="3" t="n">
         <v>762.3200000000001</v>
       </c>
+      <c r="C23" s="3" t="n">
+        <v>762.3200000000001</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -653,6 +801,12 @@
       <c r="B24" s="3" t="n">
         <v>819.72</v>
       </c>
+      <c r="C24" s="3" t="n">
+        <v>819.72</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -661,6 +815,12 @@
       <c r="B25" s="3" t="n">
         <v>853.88</v>
       </c>
+      <c r="C25" s="3" t="n">
+        <v>853.88</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -669,6 +829,12 @@
       <c r="B26" s="3" t="n">
         <v>923.12</v>
       </c>
+      <c r="C26" s="3" t="n">
+        <v>923.12</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -677,6 +843,12 @@
       <c r="B27" s="3" t="n">
         <v>1014.08</v>
       </c>
+      <c r="C27" s="3" t="n">
+        <v>1014.08</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -685,6 +857,12 @@
       <c r="B28" s="3" t="n">
         <v>1142.52</v>
       </c>
+      <c r="C28" s="3" t="n">
+        <v>1142.52</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -693,6 +871,12 @@
       <c r="B29" s="3" t="n">
         <v>1235.82</v>
       </c>
+      <c r="C29" s="3" t="n">
+        <v>1235.82</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -701,6 +885,12 @@
       <c r="B30" s="3" t="n">
         <v>1344.71</v>
       </c>
+      <c r="C30" s="3" t="n">
+        <v>1344.71</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -709,6 +899,12 @@
       <c r="B31" s="3" t="n">
         <v>1507.06</v>
       </c>
+      <c r="C31" s="3" t="n">
+        <v>1507.06</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -717,6 +913,12 @@
       <c r="B32" s="3" t="n">
         <v>1690.83</v>
       </c>
+      <c r="C32" s="3" t="n">
+        <v>1690.83</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -725,6 +927,12 @@
       <c r="B33" s="3" t="n">
         <v>1910.87</v>
       </c>
+      <c r="C33" s="3" t="n">
+        <v>1910.87</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -733,6 +941,12 @@
       <c r="B34" s="3" t="n">
         <v>2122.76</v>
       </c>
+      <c r="C34" s="3" t="n">
+        <v>2122.76</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -741,6 +955,12 @@
       <c r="B35" s="3" t="n">
         <v>2289.84</v>
       </c>
+      <c r="C35" s="3" t="n">
+        <v>2289.84</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -749,6 +969,12 @@
       <c r="B36" s="3" t="n">
         <v>2576.06</v>
       </c>
+      <c r="C36" s="3" t="n">
+        <v>2576.06</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -757,6 +983,12 @@
       <c r="B37" s="3" t="n">
         <v>2649.25</v>
       </c>
+      <c r="C37" s="3" t="n">
+        <v>2649.25</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -765,6 +997,12 @@
       <c r="B38" s="3" t="n">
         <v>2851.36</v>
       </c>
+      <c r="C38" s="3" t="n">
+        <v>2851.36</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -773,6 +1011,12 @@
       <c r="B39" s="3" t="n">
         <v>3193.77</v>
       </c>
+      <c r="C39" s="3" t="n">
+        <v>3193.77</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -781,6 +1025,12 @@
       <c r="B40" s="3" t="n">
         <v>3395.53</v>
       </c>
+      <c r="C40" s="3" t="n">
+        <v>3395.53</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -789,6 +1039,12 @@
       <c r="B41" s="3" t="n">
         <v>3559.99</v>
       </c>
+      <c r="C41" s="3" t="n">
+        <v>3559.99</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -797,6 +1053,12 @@
       <c r="B42" s="3" t="n">
         <v>3797.93</v>
       </c>
+      <c r="C42" s="3" t="n">
+        <v>3797.93</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -805,6 +1067,12 @@
       <c r="B43" s="3" t="n">
         <v>4103.23</v>
       </c>
+      <c r="C43" s="3" t="n">
+        <v>4103.23</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -812,6 +1080,502 @@
       </c>
       <c r="B44" s="3" t="n">
         <v>4363.57</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>4363.57</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>4239.199533837686</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>4118.373874531545</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>4000.991988001435</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>3886.955719840404</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>3776.169713238273</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>3668.541329244556</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>3563.980569303981</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>3462.4</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>3462.4</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>3626.1</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>3626.1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>3791.6</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>3791.6</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>4015.6</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>4015.6</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>3996</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>3996</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>3999.1</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>3999.1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>4219</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>4219</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>4546</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>4546</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>4866.7</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>4866.7</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>5207.1</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>5207.1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>5393.400000000001</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>5393.400000000001</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>5390.8</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>5390.8</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>4992.5</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>4992.5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>5229.8</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>5229.8</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>5485.599999999999</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>5485.599999999999</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>5691.4</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>5691.4</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>5976.6</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>5976.6</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>6221.5</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>6221.5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>6345</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>6345</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>6373.8</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>6373.8</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>6698.2</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>6698.2</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>7084.9</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>7084.9</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>7296</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>7296</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>7105.6</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>7105.6</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>8119.700000000001</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>8119.700000000001</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>9136.6</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>9136.6</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>9559.6</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>9559.6</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>9857</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>9857</v>
       </c>
     </row>
   </sheetData>
@@ -825,7 +1589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B83"/>
+  <dimension ref="A1:B88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -924,7 +1688,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1929–2025</t>
+          <t>1948-1989</t>
         </is>
       </c>
     </row>
@@ -936,7 +1700,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>book_period_validated</t>
+          <t>validated_book_and_extension</t>
         </is>
       </c>
     </row>
@@ -948,7 +1712,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fig_5_4</t>
+          <t>Fig_5_4, Fig_5_8</t>
         </is>
       </c>
     </row>
@@ -990,166 +1754,175 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S503-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S503-EXT</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BEA GDPbyIndustry</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>S503-COMBINED</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># S503 — Gross Final Product (GFP = TP* - C*_m)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: 5 — The Marxian Categories: Empirical Estimates</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>**Source Table**: Appendix H.1 (cross-checked vs. Appendix E.2 column `GFP` for 1948-1961 overlap)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Units**: billions_usd</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Period**: 1948-1989 (book period; extension via n/a (book period only) when API access provisioned)</t>
+          <t># S503 — Gross Final Product (GFP = TP* - C*_m)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>**Content Type**: time_series</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Chapter**: 5 — The Marxian Categories: Empirical Estimates</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>**Source Table**: Appendix H.1 (cross-checked vs. Appendix E.2 column `GFP` for 1948-1961 overlap)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>**Units**: billions_usd</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>**Period**: 1948-1989 (book period; extension via n/a (book period only) when API access provisioned)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>**Content Type**: time_series</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>**Status**: validated_book_and_extension</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Gross Final Product: GFP = TP* - C*_m. Identity-checked year-by-year against S501 and S502.</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>## Subseries</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Gross Final Product: GFP = TP* - C*_m. Identity-checked year-by-year against S501 and S502.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>| Subseries | Source | Period | Units |</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>|---|---|---|---|</t>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>| `S503-A` | S&amp;T 1994 | 1948-1989 | billions_dollars |</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>| `S503-COMBINED` |  | 1948-1989 | billions_dollars |</t>
+          <t>## Subseries</t>
         </is>
       </c>
     </row>
@@ -1161,207 +1934,203 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>| Subseries | Source | Period | Units |</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>|---|---|---|---|</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>## Construction</t>
+          <t>| `S503-A` | S&amp;T 1994 | 1948-1989 | billions_dollars |</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>| `S503-COMBINED` |  | 1948-1989 | billions_dollars |</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>### S503-A (book period, 1948-1989)</t>
-        </is>
-      </c>
+      <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>1. Read `data/source/book_tables/book_tableH1_1948_1989.csv`.</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2. Extract column `GFP_star` (and the `year` index).</t>
+          <t>## Construction</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>3. No further transformation — this is the canonical published value.</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>### S503-A (book period, 1948-1989)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Reference cross-check: Appendix E.2 column `GFP` provides the same values for 1948-1961 — V03 validates the H.1-derived series against E.2 row-by-row.</t>
-        </is>
-      </c>
+      <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1. Read `data/source/book_tables/book_tableH1_1948_1989.csv`.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>2. Extract column `GFP_star` (and the `year` index).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>3. No further transformation — this is the canonical published value.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>## Reference Values (Validation Benchmarks)</t>
-        </is>
-      </c>
+      <c r="B54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Reference cross-check: Appendix E.2 column `GFP` provides the same values for 1948-1961 — V03 validates the H.1-derived series against E.2 row-by-row.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>1948=247.74</t>
-        </is>
-      </c>
+      <c r="B56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Tolerance class: `dollar_series` (rel 0.01 / abs 1.0).</t>
-        </is>
-      </c>
+      <c r="B58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>## Reference Values (Validation Benchmarks)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Validator: `code/V03_validators/V03_S503_gross_final_product.py` writes to `data/intermediate/validation/S503.json`.</t>
-        </is>
-      </c>
+      <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
-      <c r="B61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1948=247.74</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Tolerance class: `dollar_series` (rel 0.01 / abs 1.0).</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>## Provenance Chain</t>
-        </is>
-      </c>
+      <c r="B64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Validator: `code/V03_validators/V03_S503_gross_final_product.py` writes to `data/intermediate/validation/S503.json`.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="B66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>data/source/book_tables/book_tableH1_1948_1989.csv</t>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  └── code/L01_loaders/L01_S503_gross_final_product.py</t>
-        </is>
-      </c>
+      <c r="B68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">       └── data/intermediate/S503.csv</t>
+          <t>## Provenance Chain</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            └── code/P02_processors/P02_S503_gross_final_product.py</t>
-        </is>
-      </c>
+      <c r="B70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 └── data/final/S503.csv</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1369,7 +2138,7 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">                      └── code/V03_validators/V03_S503_gross_final_product.py</t>
+          <t>data/source/book_tables/book_tableH1_1948_1989.csv</t>
         </is>
       </c>
     </row>
@@ -1377,65 +2146,105 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">  └── code/L01_loaders/L01_S503_gross_final_product.py</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
-      <c r="B74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       └── data/intermediate/S503.csv</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>---</t>
+          <t xml:space="preserve">            └── code/P02_processors/P02_S503_gross_final_product.py</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
-      <c r="B76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                 └── data/final/S503.csv</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>## Citations</t>
+          <t xml:space="preserve">                      └── code/V03_validators/V03_S503_gross_final_product.py</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
-      <c r="B78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Appendix H (Annual Time Series), p. 324-327. Cross-check vs. Appendix E.2 (Revenue Accounts, p. 310).</t>
-        </is>
-      </c>
+      <c r="B79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
-      <c r="B80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
-      <c r="B82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>## Citations</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
-      <c r="B83" t="inlineStr">
+      <c r="B83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Appendix H (Annual Time Series), p. 324-327. Cross-check vs. Appendix E.2 (Revenue Accounts, p. 310).</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard).*</t>
         </is>
@@ -1452,10 +2261,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1480,180 +2289,313 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GFP = TP* - C*_m. Gross Final Product is the Marxian value-added of productive sectors, analogous to but distinct from conventional GDP. GFP represents the new value created in production, before decomposition into variable capital and surplus value.</t>
+          <t>GVA* = TV* - C*m = Marxian gross value added.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5; Knowledge_Base/equations/page_310_equations.txt</t>
+          <t>ST_1994, Ch5, p.95; chunk_12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Derived series: GFP = S501 - S502. For the book period (1948-1989), both components come from Table E.2. Extension is limited by S502 availability (no extension), so GFP extension would require either extending C*_m or approximating it.</t>
+          <t>Marxian gross value added GVA*: GVA* = TV* - C*m. Sum of downward hatched elements (including M'tt) within the dashed rectangle of Figure 5.2.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Knowledge_Base/tables/page_310_table_E2.csv</t>
+          <t>ST_1994, Ch5, p.92; chunk_12</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>figure_context</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fig 5.4 shows GFP as the value-added layer in the revenue account, decomposed into V* and S*. GFP is the key bridge between total product and the distribution categories.</t>
+          <t>GFD and GFP* surprisingly close: roughly equal in 1947, roughly 11% apart by 1977.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ST_1994, Fig 5.4</t>
+          <t>ST_1994, Ch5, p.94; chunk_12</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>theoretical_note</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GFP differs from GDP in two fundamental ways: (1) it excludes value added by unproductive sectors (FIRE, government, most services), and (2) it measures the value created in production rather than the income generated across all sectors. The ratio GFP/GDP reveals the productive core of the economy.</t>
+          <t>GVA* = TV* − C*m = Marxian gross value added.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5 p.220; Technical/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_22/full_transcription.md</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Extension beyond 1989 is blocked by S502 (C*_m) unavailability. A proxy GFP extension could use BEA value-added by industry for productive sectors, but this would not be strictly comparable to the book methodology.</t>
+          <t>Marxian gross value added GVA*: GVA* = TV* − C*m. Sum of downward hatched elements (including M′tt) within the dashed rectangle of Figure 5.2.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DPR T503_DPR.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+          <t>ST_1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>GFD and GFP* surprisingly close: roughly equal in 1947, roughly 11% apart by 1977.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ST_1994</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gross Final Product is the Marxian value-added: GFP = TP* - C*_m. Derived from S501 and S502. Book period only (1948-1989) due to C*_m extension constraint.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+          <t>GFP = TP* - C*_m. Gross Final Product is the Marxian value-added of productive sectors, analogous to but distinct from conventional GDP. GFP represents the new value created in production, before decomposition into variable capital and surplus value.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5; Knowledge_Base/equations/page_310_equations.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>data_source</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Derived series: GFP = S501 - S502. For the book period (1948-1989), both components come from Table E.2. Extension is limited by S502 availability (no extension), so GFP extension would require either extending C*_m or approximating it.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Knowledge_Base/tables/page_310_table_E2.csv</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>figure_context</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fig 5.4 shows GFP as the value-added layer in the revenue account, decomposed into V* and S*. GFP is the key bridge between total product and the distribution categories.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ST_1994, Fig 5.4</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>theoretical_note</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Extension blocked by S502 availability</t>
+          <t>GFP differs from GDP in two fundamental ways: (1) it excludes value added by unproductive sectors (FIRE, government, most services), and (2) it measures the value created in production rather than the income generated across all sectors. The ratio GFP/GDP reveals the productive core of the economy.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5 p.220; Technical/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_22/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>caveat</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Proxy via BEA value-added would break strict methodology comparability</t>
+          <t>Extension beyond 1989 is blocked by S502 (C*_m) unavailability. A proxy GFP extension could use BEA value-added by industry for productive sectors, but this would not be strictly comparable to the book methodology.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DPR T503_DPR.md</t>
         </is>
       </c>
     </row>
     <row r="13"/>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
-      </c>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr"/>
+      <c r="C14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>S501</t>
-        </is>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="n">
+        <v>95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>S502</t>
-        </is>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="n">
+        <v>92</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>S504</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>S505</t>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Gross Final Product is the Marxian value-added: GFP = TP* - C*_m. Derived from S501 and S502. Book period only (1948-1989) due to C*_m extension constraint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Extension blocked by S502 availability</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Proxy via BEA value-added would break strict methodology comparability</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>S501</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>S502</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>S504</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>S505</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>citations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
@@ -1670,11 +2612,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -1751,59 +2693,178 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>EXTENSION</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>null — series does not extend beyond book period</t>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
+      <c r="B5" s="4" t="inlineStr"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BEA</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VALIDATION</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>splice_year</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>reference_values</t>
+          <t>splice_method</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>growth_rate</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>expected_range</t>
+          <t>output_subseries</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[0, 30000]</t>
+          <t>S503-EXT</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>combined_subseries</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>S503-COMBINED</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). Measuring the Wealth of Nations. Cambridge University Press. Ch. 5, Appendix H.1 (column GFP_star), pp. 324-327. GFP is defined by the identity GFP = TP* - C*_m: total value added by productive industries, i.e. productive-sector net product at market prices before separation of V (variable capital) from S (surplus value).", "shaikh_appendix_ref": "Appendix H.1, column GFP_star (1948-1989); pp. 324-327. Figures 5.4, 5.6, 9.1 plot GFP* as the Marxian net product aggregate.", "extension_source": "BEA GDP-by-Industry Value Added (TableID=1) for productive+trade top-level NAICS industries (S503-EXT subseries). Industries: 11 (Agriculture), 21 (Mining), 22 (Utilities), 23 (Construction), 31G (Manufacturing rollup), 42 (Wholesale), 44RT (Retail), 48TW (Transportation+Warehousing). Cache file: gdp_by_industry_value_added.csv at Inputs/ST2/Inputs/API_Data/BEA/, pulled 2026-02-24 by pull_bea_nipa_ch05.py.", "extension_url": "https://www.bea.gov/data/gdp/gdp-industry", "conceptual_continuity": "GFP is value added by productive industries. BEA's industry-level Value Added (VA = GO - II) is the directly published modern equivalent restricted to the productive partition. Both eras observe the same construct under different industrial classifications (SIC vs NAICS). Growth-rate splice is admissible per the Anu Extension Standard because VA is a directly-observed level, not a derived ratio. The only methodological adjustment is the SIC&lt;-&gt;NAICS productive-industry concordance (per S501 EPR Appendix C).", "vintage_note": "Book values 1948-1989 frozen at the book's vintage (SIC-based BEA NIPA + IO tables as published by 1993). Modern extension uses BEA GDP-by-Industry NAICS data 1997-2024, approximately the September 2025 NIPA vintage. IMPORTANT DIVERGENCE: the 1989 book endpoint (4363.57) exceeds the 1997 BEA endpoint (3462.40) by ~26%, a downward discontinuity at the SIC-&gt;NAICS junction. This reflects (a) BEA's tighter NAICS productive-sector definition (some services reclassified out of productive industries between SIC 1987 and NAICS 1997), (b) comprehensive revisions to deflators and concepts, and (c) possible scope differences in book's productive-trade boundary vs BEA's published industry rollups. The growth-rate splice methodology still preserves the BEA post-1997 growth profile, and the log-linear bridge fills 1990-1996 with monotone interpolation, but users should treat the 1989-1997 transition as a vintage discontinuity rather than a true real decline. See DIVERGENCE_REGISTER M04_S503 and a future variant VPR may explore an alternative SIC-extension or rescaled-level splice."}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>depends_on</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>["gdp_by_industry_value_added.csv"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>reference_values</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>{"1948": 247.74, "1989": 4363.57, "1997": 3462.4, "2010": 5229.8, "2024": 9857.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>expected_range</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>[0, 30000]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>tolerance</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>level_series</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>dollar_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>dollar_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1.0</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S503.xlsx
+++ b/extenbooks/S503.xlsx
@@ -589,10 +589,10 @@
         <v>1954</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>335.2</v>
+        <v>335.26</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>335.2</v>
+        <v>335.26</v>
       </c>
       <c r="D9" s="3" t="n">
         <v/>
@@ -2612,10 +2612,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -2868,6 +2868,18 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>extension_year_range</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>[1948, 2024]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S503.xlsx
+++ b/extenbooks/S503.xlsx
@@ -1096,7 +1096,7 @@
         <v/>
       </c>
       <c r="C45" s="3" t="n">
-        <v>4239.199533837686</v>
+        <v>2861.281</v>
       </c>
       <c r="D45" s="3" t="n">
         <v/>
@@ -1110,7 +1110,7 @@
         <v/>
       </c>
       <c r="C46" s="3" t="n">
-        <v>4118.373874531545</v>
+        <v>2882.873</v>
       </c>
       <c r="D46" s="3" t="n">
         <v/>
@@ -1124,7 +1124,7 @@
         <v/>
       </c>
       <c r="C47" s="3" t="n">
-        <v>4000.991988001435</v>
+        <v>2997.896</v>
       </c>
       <c r="D47" s="3" t="n">
         <v/>
@@ -1138,7 +1138,7 @@
         <v/>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3886.955719840404</v>
+        <v>3133.242</v>
       </c>
       <c r="D48" s="3" t="n">
         <v/>
@@ -1152,7 +1152,7 @@
         <v/>
       </c>
       <c r="C49" s="3" t="n">
-        <v>3776.169713238273</v>
+        <v>3389.034</v>
       </c>
       <c r="D49" s="3" t="n">
         <v/>
@@ -1166,7 +1166,7 @@
         <v/>
       </c>
       <c r="C50" s="3" t="n">
-        <v>3668.541329244556</v>
+        <v>3541.579</v>
       </c>
       <c r="D50" s="3" t="n">
         <v/>
@@ -1180,7 +1180,7 @@
         <v/>
       </c>
       <c r="C51" s="3" t="n">
-        <v>3563.980569303981</v>
+        <v>3749.167</v>
       </c>
       <c r="D51" s="3" t="n">
         <v/>
@@ -1589,7 +1589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B88"/>
+  <dimension ref="A1:B98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2247,78 @@
       <c r="B88" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard).*</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>## WP-A REBUILD ADDENDUM (2026-07-01, comprehensive review)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>**Provenance corrected + real SIC fill (DIV-A12).** S503-EXT is a RAW pass-through of BEA</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>GDP-by-Industry VA (the pre-review 'growth_rate splice at 1997' label was FALSE). S503-COMBINED</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1990-96 now = real SIC-basis partition-A VA (2861-&gt;3749), replacing the log-linear bridge; this</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>EXPOSES the DIV-007 book-GFP-vs-BEA-VA concept break at the 1989/1990 seam (book GFP* is an I-O</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>final-demand transform ~1.571x BEA industry VA - DIV-A10). Extension refvals re-anchored to BEA</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>table sums (cross-table verified). V03 PASS 5/5.</t>
         </is>
       </c>
     </row>
@@ -2612,14 +2684,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2672,170 +2744,179 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>derive</t>
+          <t>extend</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>S501-A, S502-A</t>
+          <t>BEA_GDPbyIndustry_VA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>S503-EXT</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>BEA GDP-by-Industry Value Added, productive+trade NAICS partition A [11,21,22,23,31G,42,44RT,48TW], raw sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>combine</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>S503-A, BEA_SIC_partitionA_VA, S503-EXT</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>S503-COMBINED</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>GFP = TP* - C*_m</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>EXTENSION</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BEA</t>
-        </is>
-      </c>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>splice_year</t>
+          <t>api</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>BEA</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>splice_method</t>
+          <t>splice_year</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>growth_rate</t>
+          <t>1997</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>output_subseries</t>
+          <t>splice_method</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S503-EXT</t>
+          <t>none (raw pass-through; DIV-007 junction -20.7% at 1997 disclosed)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>combined_subseries</t>
+          <t>output_subseries</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S503-COMBINED</t>
+          <t>S503-EXT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>provenance</t>
+          <t>combined_subseries</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). Measuring the Wealth of Nations. Cambridge University Press. Ch. 5, Appendix H.1 (column GFP_star), pp. 324-327. GFP is defined by the identity GFP = TP* - C*_m: total value added by productive industries, i.e. productive-sector net product at market prices before separation of V (variable capital) from S (surplus value).", "shaikh_appendix_ref": "Appendix H.1, column GFP_star (1948-1989); pp. 324-327. Figures 5.4, 5.6, 9.1 plot GFP* as the Marxian net product aggregate.", "extension_source": "BEA GDP-by-Industry Value Added (TableID=1) for productive+trade top-level NAICS industries (S503-EXT subseries). Industries: 11 (Agriculture), 21 (Mining), 22 (Utilities), 23 (Construction), 31G (Manufacturing rollup), 42 (Wholesale), 44RT (Retail), 48TW (Transportation+Warehousing). Cache file: gdp_by_industry_value_added.csv at Inputs/ST2/Inputs/API_Data/BEA/, pulled 2026-02-24 by pull_bea_nipa_ch05.py.", "extension_url": "https://www.bea.gov/data/gdp/gdp-industry", "conceptual_continuity": "GFP is value added by productive industries. BEA's industry-level Value Added (VA = GO - II) is the directly published modern equivalent restricted to the productive partition. Both eras observe the same construct under different industrial classifications (SIC vs NAICS). Growth-rate splice is admissible per the Anu Extension Standard because VA is a directly-observed level, not a derived ratio. The only methodological adjustment is the SIC&lt;-&gt;NAICS productive-industry concordance (per S501 EPR Appendix C).", "vintage_note": "Book values 1948-1989 frozen at the book's vintage (SIC-based BEA NIPA + IO tables as published by 1993). Modern extension uses BEA GDP-by-Industry NAICS data 1997-2024, approximately the September 2025 NIPA vintage. IMPORTANT DIVERGENCE: the 1989 book endpoint (4363.57) exceeds the 1997 BEA endpoint (3462.40) by ~26%, a downward discontinuity at the SIC-&gt;NAICS junction. This reflects (a) BEA's tighter NAICS productive-sector definition (some services reclassified out of productive industries between SIC 1987 and NAICS 1997), (b) comprehensive revisions to deflators and concepts, and (c) possible scope differences in book's productive-trade boundary vs BEA's published industry rollups. The growth-rate splice methodology still preserves the BEA post-1997 growth profile, and the log-linear bridge fills 1990-1996 with monotone interpolation, but users should treat the 1989-1997 transition as a vintage discontinuity rather than a true real decline. See DIVERGENCE_REGISTER M04_S503 and a future variant VPR may explore an alternative SIC-extension or rescaled-level splice."}</t>
+          <t>S503-COMBINED</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). Measuring the Wealth of Nations. Cambridge University Press. Ch. 5, Appendix H.1 (column GFP_star), pp. 324-327. GFP is defined by the identity GFP = TP* - C*_m: total value added by productive industries, i.e. productive-sector net product at market prices before separation of V (variable capital) from S (surplus value).", "shaikh_appendix_ref": "Appendix H.1, column GFP_star (1948-1989); pp. 324-327. Figures 5.4, 5.6, 9.1 plot GFP* as the Marxian net product aggregate.", "extension_source": "BEA GDP-by-Industry Value Added (TableID=1) for productive+trade top-level NAICS industries (S503-EXT subseries). Industries: 11 (Agriculture), 21 (Mining), 22 (Utilities), 23 (Construction), 31G (Manufacturing rollup), 42 (Wholesale), 44RT (Retail), 48TW (Transportation+Warehousing). Cache file: gdp_by_industry_value_added.csv at Inputs/ST2/Inputs/API_Data/BEA/, pulled 2026-02-24 by pull_bea_nipa_ch05.py.", "extension_url": "https://www.bea.gov/data/gdp/gdp-industry", "conceptual_continuity": "GFP is value added by productive industries. BEA's industry-level Value Added (VA = GO - II) is the directly published modern equivalent restricted to the productive partition. Both eras observe the same construct under different industrial classifications (SIC vs NAICS). Growth-rate splice is admissible per the Anu Extension Standard because VA is a directly-observed level, not a derived ratio. The only methodological adjustment is the SIC&lt;-&gt;NAICS productive-industry concordance (per S501 EPR Appendix C).", "vintage_note": "Book values 1948-1989 frozen at the book's vintage (SIC-based BEA NIPA + IO tables as published by 1993). Modern extension uses BEA GDP-by-Industry NAICS data 1997-2024, approximately the September 2025 NIPA vintage. IMPORTANT DIVERGENCE: the 1989 book endpoint (4363.57) exceeds the 1997 BEA endpoint (3462.40) by ~26%, a downward discontinuity at the SIC-&gt;NAICS junction. This reflects (a) BEA's tighter NAICS productive-sector definition (some services reclassified out of productive industries between SIC 1987 and NAICS 1997), (b) comprehensive revisions to deflators and concepts, and (c) possible scope differences in book's productive-trade boundary vs BEA's published industry rollups. The growth-rate splice methodology still preserves the BEA post-1997 growth profile, and the log-linear bridge fills 1990-1996 with monotone interpolation, but users should treat the 1989-1997 transition as a vintage discontinuity rather than a true real decline. See DIVERGENCE_REGISTER M04_S503 and a future variant VPR may explore an alternative SIC-extension or rescaled-level splice."}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>depends_on</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>["gdp_by_industry_value_added.csv"]</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>VALIDATION</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>reference_values</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{"1948": 247.74, "1989": 4363.57, "1997": 3462.4, "2010": 5229.8, "2024": 9857.0}</t>
-        </is>
-      </c>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>expected_range</t>
+          <t>reference_values</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[0, 30000]</t>
+          <t>{"1948": 247.74, "1989": 4363.57, "1997": 3462.4, "2010": 5229.8, "2024": 9857.0}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>tolerance</t>
+          <t>expected_range</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>dollar_series</t>
+          <t>[0, 30000]</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tolerance_class</t>
+          <t>tolerance</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2847,36 +2928,60 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tolerance_rel</t>
+          <t>tolerance_class</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>dollar_series</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tolerance_abs</t>
+          <t>tolerance_rel</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.01</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>extension_year_range</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>[1948, 2024]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>reference_source</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1997/2010/2024 = BEA GDP-by-Industry Value Added over partition-A NAICS; cross-verified vs va_components (rounding-level). class=external (de-tautologized DIV-022).</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S503.xlsx
+++ b/extenbooks/S503.xlsx
@@ -2864,7 +2864,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). Measuring the Wealth of Nations. Cambridge University Press. Ch. 5, Appendix H.1 (column GFP_star), pp. 324-327. GFP is defined by the identity GFP = TP* - C*_m: total value added by productive industries, i.e. productive-sector net product at market prices before separation of V (variable capital) from S (surplus value).", "shaikh_appendix_ref": "Appendix H.1, column GFP_star (1948-1989); pp. 324-327. Figures 5.4, 5.6, 9.1 plot GFP* as the Marxian net product aggregate.", "extension_source": "BEA GDP-by-Industry Value Added (TableID=1) for productive+trade top-level NAICS industries (S503-EXT subseries). Industries: 11 (Agriculture), 21 (Mining), 22 (Utilities), 23 (Construction), 31G (Manufacturing rollup), 42 (Wholesale), 44RT (Retail), 48TW (Transportation+Warehousing). Cache file: gdp_by_industry_value_added.csv at Inputs/ST2/Inputs/API_Data/BEA/, pulled 2026-02-24 by pull_bea_nipa_ch05.py.", "extension_url": "https://www.bea.gov/data/gdp/gdp-industry", "conceptual_continuity": "GFP is value added by productive industries. BEA's industry-level Value Added (VA = GO - II) is the directly published modern equivalent restricted to the productive partition. Both eras observe the same construct under different industrial classifications (SIC vs NAICS). Growth-rate splice is admissible per the Anu Extension Standard because VA is a directly-observed level, not a derived ratio. The only methodological adjustment is the SIC&lt;-&gt;NAICS productive-industry concordance (per S501 EPR Appendix C).", "vintage_note": "Book values 1948-1989 frozen at the book's vintage (SIC-based BEA NIPA + IO tables as published by 1993). Modern extension uses BEA GDP-by-Industry NAICS data 1997-2024, approximately the September 2025 NIPA vintage. IMPORTANT DIVERGENCE: the 1989 book endpoint (4363.57) exceeds the 1997 BEA endpoint (3462.40) by ~26%, a downward discontinuity at the SIC-&gt;NAICS junction. This reflects (a) BEA's tighter NAICS productive-sector definition (some services reclassified out of productive industries between SIC 1987 and NAICS 1997), (b) comprehensive revisions to deflators and concepts, and (c) possible scope differences in book's productive-trade boundary vs BEA's published industry rollups. The growth-rate splice methodology still preserves the BEA post-1997 growth profile, and the log-linear bridge fills 1990-1996 with monotone interpolation, but users should treat the 1989-1997 transition as a vintage discontinuity rather than a true real decline. See DIVERGENCE_REGISTER M04_S503 and a future variant VPR may explore an alternative SIC-extension or rescaled-level splice."}</t>
+          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). Measuring the Wealth of Nations. Cambridge University Press. Ch. 5, Appendix H.1 (column GFP_star), pp. 324-327. GFP is defined by the identity GFP = TP* - C*_m: total value added by productive industries, i.e. productive-sector net product at market prices before separation of V (variable capital) from S (surplus value).", "shaikh_appendix_ref": "Appendix H.1, column GFP_star (1948-1989); pp. 324-327. Figures 5.4, 5.6, 9.1 plot GFP* as the Marxian net product aggregate.", "extension_source": "BEA GDP-by-Industry Value Added (TableID=1) for productive+trade top-level NAICS industries (S503-EXT subseries). Industries: 11 (Agriculture), 21 (Mining), 22 (Utilities), 23 (Construction), 31G (Manufacturing rollup), 42 (Wholesale), 44RT (Retail), 48TW (Transportation+Warehousing). Cache file: gdp_by_industry_value_added.csv at data/raw/Inputs/API_Data/BEA/, pulled 2026-02-24 by pull_bea_nipa_ch05.py.", "extension_url": "https://www.bea.gov/data/gdp/gdp-industry", "conceptual_continuity": "GFP is value added by productive industries. BEA's industry-level Value Added (VA = GO - II) is the directly published modern equivalent restricted to the productive partition. Both eras observe the same construct under different industrial classifications (SIC vs NAICS). Growth-rate splice is admissible per the Anu Extension Standard because VA is a directly-observed level, not a derived ratio. The only methodological adjustment is the SIC&lt;-&gt;NAICS productive-industry concordance (per S501 EPR Appendix C).", "vintage_note": "Book values 1948-1989 frozen at the book's vintage (SIC-based BEA NIPA + IO tables as published by 1993). Modern extension uses BEA GDP-by-Industry NAICS data 1997-2024, approximately the September 2025 NIPA vintage. IMPORTANT DIVERGENCE: the 1989 book endpoint (4363.57) exceeds the 1997 BEA endpoint (3462.40) by ~26%, a downward discontinuity at the SIC-&gt;NAICS junction. This reflects (a) BEA's tighter NAICS productive-sector definition (some services reclassified out of productive industries between SIC 1987 and NAICS 1997), (b) comprehensive revisions to deflators and concepts, and (c) possible scope differences in book's productive-trade boundary vs BEA's published industry rollups. The growth-rate splice methodology still preserves the BEA post-1997 growth profile, and the log-linear bridge fills 1990-1996 with monotone interpolation, but users should treat the 1989-1997 transition as a vintage discontinuity rather than a true real decline. See DIVERGENCE_REGISTER M04_S503 and a future variant VPR may explore an alternative SIC-extension or rescaled-level splice."}</t>
         </is>
       </c>
     </row>
